--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:57</t>
+    <t xml:space="preserve">2026-09-09 22:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:48</t>
+    <t xml:space="preserve">2026-09-18 10:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:10</t>
+    <t xml:space="preserve">2026-09-23 12:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:14</t>
+    <t xml:space="preserve">2026-10-02 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:49</t>
+    <t xml:space="preserve">2026-10-05 09:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
